--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487937_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487937_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3977</v>
+        <v>6.4148</v>
       </c>
       <c r="E2" t="n">
-        <v>2.119</v>
+        <v>1.3347</v>
       </c>
       <c r="F2" t="n">
-        <v>4.2787</v>
+        <v>5.0801</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8884</v>
+        <v>4.954</v>
       </c>
       <c r="H2" t="n">
-        <v>1.791</v>
+        <v>0.9021</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0974</v>
+        <v>4.0519</v>
       </c>
       <c r="J2" t="n">
-        <v>3.611</v>
+        <v>2.6396</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6606</v>
+        <v>0.0532</v>
       </c>
       <c r="L2" t="n">
-        <v>1.9504</v>
+        <v>2.5864</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2774</v>
+        <v>2.3144</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1304</v>
+        <v>0.849</v>
       </c>
       <c r="O2" t="n">
-        <v>0.147</v>
+        <v>1.4655</v>
       </c>
       <c r="P2" t="n">
+        <v>1.0406</v>
+      </c>
+      <c r="Q2" t="n">
         <v>-1.0406</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>-3.1218</v>
       </c>
       <c r="R2" t="n">
         <v>2.0812</v>
       </c>
       <c r="S2" t="n">
-        <v>1.2148</v>
+        <v>0.4202</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7053</v>
+        <v>-0.2643</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9201</v>
+        <v>0.6844</v>
       </c>
       <c r="V2" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3351</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.9782</v>
+        <v>6.3463</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4403</v>
+        <v>2.6548</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5379</v>
+        <v>3.6915</v>
       </c>
       <c r="G3" t="n">
-        <v>3.8019</v>
+        <v>3.8884</v>
       </c>
       <c r="H3" t="n">
-        <v>2.5479</v>
+        <v>1.791</v>
       </c>
       <c r="I3" t="n">
-        <v>1.254</v>
+        <v>2.0974</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2142</v>
+        <v>3.611</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6052</v>
+        <v>1.6606</v>
       </c>
       <c r="L3" t="n">
-        <v>0.609</v>
+        <v>1.9504</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5877</v>
+        <v>0.2774</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0573</v>
+        <v>0.1304</v>
       </c>
       <c r="O3" t="n">
-        <v>0.645</v>
+        <v>0.147</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2081</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-3.1218</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2893</v>
+        <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3844</v>
+        <v>1.1634</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7235</v>
+        <v>-0.1695</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6609</v>
+        <v>1.3329</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5838</v>
+        <v>2.3351</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5838</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.6632</v>
+        <v>5.3059</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9061</v>
+        <v>1.7973</v>
       </c>
       <c r="F4" t="n">
-        <v>4.7571</v>
+        <v>3.5086</v>
       </c>
       <c r="G4" t="n">
-        <v>4.954</v>
+        <v>3.8019</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9021</v>
+        <v>2.5479</v>
       </c>
       <c r="I4" t="n">
-        <v>4.0519</v>
+        <v>1.254</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6396</v>
+        <v>3.2142</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0532</v>
+        <v>2.6052</v>
       </c>
       <c r="L4" t="n">
-        <v>2.5864</v>
+        <v>0.609</v>
       </c>
       <c r="M4" t="n">
-        <v>2.3144</v>
+        <v>0.5877</v>
       </c>
       <c r="N4" t="n">
-        <v>0.849</v>
+        <v>-0.0573</v>
       </c>
       <c r="O4" t="n">
-        <v>1.4655</v>
+        <v>0.645</v>
       </c>
       <c r="P4" t="n">
-        <v>1.0406</v>
+        <v>0.2081</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0812</v>
+        <v>2.2893</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3314</v>
+        <v>0.7121</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6929</v>
+        <v>0.0805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3615</v>
+        <v>0.6316000000000001</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>5.4703</v>
+        <v>3.9011</v>
       </c>
       <c r="E5" t="n">
-        <v>5.7528</v>
+        <v>4.3597</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.2824</v>
+        <v>-0.4586</v>
       </c>
       <c r="G5" t="n">
         <v>3.6088</v>
@@ -844,13 +844,13 @@
         <v>1.2487</v>
       </c>
       <c r="S5" t="n">
-        <v>2.821</v>
+        <v>1.2518</v>
       </c>
       <c r="T5" t="n">
-        <v>2.466</v>
+        <v>1.073</v>
       </c>
       <c r="U5" t="n">
-        <v>0.355</v>
+        <v>0.1788</v>
       </c>
       <c r="V5" t="n">
         <v>-1.1675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.3514</v>
+        <v>3.6538</v>
       </c>
       <c r="E6" t="n">
-        <v>1.7964</v>
+        <v>2.0107</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5549</v>
+        <v>1.643</v>
       </c>
       <c r="G6" t="n">
         <v>3.2891</v>
@@ -922,13 +922,13 @@
         <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3973</v>
+        <v>0.6997</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0743</v>
+        <v>0.2886</v>
       </c>
       <c r="U6" t="n">
-        <v>0.323</v>
+        <v>0.4111</v>
       </c>
       <c r="V6" t="n">
         <v>-1.1675</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.7758</v>
+        <v>3.5846</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.768</v>
+        <v>-1.0179</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5438</v>
+        <v>4.6025</v>
       </c>
       <c r="G7" t="n">
         <v>1.9043</v>
@@ -1000,13 +1000,13 @@
         <v>2.2893</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0796</v>
+        <v>0.8884</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4319</v>
+        <v>0.3182</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5115</v>
+        <v>0.5703</v>
       </c>
       <c r="V7" t="n">
         <v>0.5838</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. GUEYE</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8681</v>
+        <v>2.0615</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9438</v>
+        <v>1.1917</v>
       </c>
       <c r="F8" t="n">
-        <v>2.8119</v>
+        <v>0.8697</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6556</v>
+        <v>0.6061</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.3201</v>
+        <v>1.7311</v>
       </c>
       <c r="I8" t="n">
-        <v>1.9757</v>
+        <v>-1.125</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.1486</v>
+        <v>1.6594</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.5527</v>
+        <v>1.5026</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4041</v>
+        <v>0.1568</v>
       </c>
       <c r="M8" t="n">
-        <v>1.8042</v>
+        <v>-1.0533</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2326</v>
+        <v>0.2284</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5716</v>
+        <v>-1.2818</v>
       </c>
       <c r="P8" t="n">
-        <v>1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R8" t="n">
         <v>1.4568</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9232</v>
+        <v>0.3316</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2048</v>
+        <v>0.5729</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7183</v>
+        <v>-0.2414</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.1675</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>D. GUEYE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.8662</v>
+        <v>1.9855</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0846</v>
+        <v>-0.9438</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7817</v>
+        <v>2.9293</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6061</v>
+        <v>0.6556</v>
       </c>
       <c r="H9" t="n">
-        <v>1.7311</v>
+        <v>-1.3201</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.125</v>
+        <v>1.9757</v>
       </c>
       <c r="J9" t="n">
-        <v>1.6594</v>
+        <v>-1.1486</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5026</v>
+        <v>-1.5527</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1568</v>
+        <v>0.4041</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0533</v>
+        <v>1.8042</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2284</v>
+        <v>0.2326</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2818</v>
+        <v>1.5716</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>1.4568</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>1.4568</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1364</v>
+        <v>1.0406</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4658</v>
+        <v>0.2048</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3294</v>
+        <v>0.8358</v>
       </c>
       <c r="V9" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.7076</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.1891</v>
+        <v>1.6676</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3216</v>
+        <v>0.5359</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8675</v>
+        <v>1.1317</v>
       </c>
       <c r="G10" t="n">
         <v>0.6097</v>
@@ -1234,13 +1234,13 @@
         <v>2.0812</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3582</v>
+        <v>0.1204</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1396</v>
+        <v>0.3539</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4978</v>
+        <v>-0.2335</v>
       </c>
       <c r="V10" t="n">
         <v>0.9376</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.6271</v>
+        <v>-2.6565</v>
       </c>
       <c r="E11" t="n">
         <v>-2.0757</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.5514</v>
+        <v>-0.5807</v>
       </c>
       <c r="G11" t="n">
         <v>0.0257</v>
@@ -1312,13 +1312,13 @@
         <v>0.8325</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1096</v>
+        <v>-0.139</v>
       </c>
       <c r="T11" t="n">
         <v>-0.4567</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3471</v>
+        <v>0.3178</v>
       </c>
       <c r="V11" t="n">
         <v>-2.3351</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0301</v>
+        <v>-3.3619</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9262</v>
+        <v>-6.1405</v>
       </c>
       <c r="F12" t="n">
-        <v>2.896</v>
+        <v>2.7786</v>
       </c>
       <c r="G12" t="n">
         <v>-0.5849</v>
@@ -1390,13 +1390,13 @@
         <v>1.0406</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6765</v>
+        <v>0.3448</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0033</v>
+        <v>-0.2176</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6798999999999999</v>
+        <v>0.5624</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>28.9028</v>
+        <v>28.9027</v>
       </c>
       <c r="E13" t="n">
-        <v>3.707100000000001</v>
+        <v>3.7069</v>
       </c>
       <c r="F13" t="n">
         <v>25.1957</v>
@@ -1468,13 +1468,13 @@
         <v>18.7307</v>
       </c>
       <c r="S13" t="n">
-        <v>6.834000000000001</v>
+        <v>6.834</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7839</v>
+        <v>1.7838</v>
       </c>
       <c r="U13" t="n">
-        <v>5.0501</v>
+        <v>5.0502</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6897</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.5527</v>
+        <v>1.4622</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7061</v>
+        <v>1.3847</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1534</v>
+        <v>0.0776</v>
       </c>
       <c r="G14" t="n">
         <v>0.3249</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1122</v>
+        <v>-0.2027</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2519</v>
+        <v>-0.5734</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1397</v>
+        <v>0.3706</v>
       </c>
       <c r="V14" t="n">
         <v>-0.1168</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4429</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1741</v>
+        <v>-1.6027</v>
       </c>
       <c r="F15" t="n">
-        <v>1.617</v>
+        <v>1.525</v>
       </c>
       <c r="G15" t="n">
         <v>-1.3598</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3001</v>
+        <v>-0.2205</v>
       </c>
       <c r="T15" t="n">
-        <v>0.152</v>
+        <v>-0.2767</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1482</v>
+        <v>0.0562</v>
       </c>
       <c r="V15" t="n">
         <v>2.3351</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0606</v>
+        <v>-1.6465</v>
       </c>
       <c r="E16" t="n">
-        <v>0.7742</v>
+        <v>-0.8331</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8349</v>
+        <v>-0.8134</v>
       </c>
       <c r="G16" t="n">
         <v>-3.3677</v>
@@ -1702,13 +1702,13 @@
         <v>2.9137</v>
       </c>
       <c r="S16" t="n">
-        <v>1.5507</v>
+        <v>-0.0351</v>
       </c>
       <c r="T16" t="n">
-        <v>1.2388</v>
+        <v>-0.3685</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3119</v>
+        <v>0.3334</v>
       </c>
       <c r="V16" t="n">
         <v>-0.1168</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2393</v>
+        <v>-1.8733</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1488</v>
+        <v>0.5774</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3881</v>
+        <v>-2.4507</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0527</v>
@@ -1780,13 +1780,13 @@
         <v>1.2487</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.019</v>
+        <v>-0.6531</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5748</v>
+        <v>-0.1462</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4442</v>
+        <v>-0.5069</v>
       </c>
       <c r="V17" t="n">
         <v>-1.1675</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2271</v>
+        <v>-2.3238</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.5254</v>
+        <v>-1.8825</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7017</v>
+        <v>-0.4413</v>
       </c>
       <c r="G18" t="n">
         <v>-2.2968</v>
@@ -1858,13 +1858,13 @@
         <v>2.4974</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3785</v>
+        <v>-0.4753</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8234</v>
+        <v>-0.1804</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5551</v>
+        <v>-0.2948</v>
       </c>
       <c r="V18" t="n">
         <v>1.2807</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. REILLY</t>
+          <t>D. RAMÍREZ SÁNCHEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.5503</v>
+        <v>-3.1046</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.2944</v>
+        <v>-4.0227</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2559</v>
+        <v>0.9181</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.6637</v>
+        <v>-2.3022</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.8912</v>
+        <v>-2.1683</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.7725</v>
+        <v>-0.1339</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1287</v>
+        <v>-1.4692</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2642</v>
+        <v>-1.2944</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1355</v>
+        <v>-0.1747</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.7924</v>
+        <v>-0.833</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1554</v>
+        <v>-0.8738</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.6369</v>
+        <v>0.0408</v>
       </c>
       <c r="P19" t="n">
-        <v>0.2081</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.2487</v>
+        <v>-2.2893</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0948</v>
+        <v>-0.4776</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1744</v>
+        <v>-0.2643</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0796</v>
+        <v>-0.2133</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.1168</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. RAMÍREZ SÁNCHEZ</t>
+          <t>J. REILLY</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.7896</v>
+        <v>-3.2773</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4514</v>
+        <v>-2.0801</v>
       </c>
       <c r="F20" t="n">
-        <v>0.6618000000000001</v>
+        <v>-1.1972</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.3022</v>
+        <v>-2.6637</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1683</v>
+        <v>-0.8912</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1339</v>
+        <v>-1.7725</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4692</v>
+        <v>0.1287</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.2944</v>
+        <v>0.2642</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1747</v>
+        <v>-0.1355</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.833</v>
+        <v>-2.7924</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8738</v>
+        <v>-1.1554</v>
       </c>
       <c r="O20" t="n">
-        <v>0.0408</v>
+        <v>-1.6369</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2081</v>
+        <v>0.2081</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.2893</v>
+        <v>-1.2487</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1626</v>
+        <v>-0.8217</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6929</v>
+        <v>-0.9601</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4697</v>
+        <v>0.1383</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.5138</v>
+        <v>-4.9091</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2752</v>
+        <v>-2.8466</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.2386</v>
+        <v>-2.0624</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2958</v>
@@ -2092,13 +2092,13 @@
         <v>1.2487</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4699</v>
+        <v>-0.8651</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8827</v>
+        <v>-0.7065</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.2122</v>
+        <v>-5.6788</v>
       </c>
       <c r="E22" t="n">
-        <v>-7.3867</v>
+        <v>-7.1724</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1745</v>
+        <v>1.4936</v>
       </c>
       <c r="G22" t="n">
         <v>-4.6909</v>
@@ -2170,13 +2170,13 @@
         <v>2.7055</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.237</v>
+        <v>-0.7036</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.2925</v>
+        <v>-1.0782</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0555</v>
+        <v>0.3745</v>
       </c>
       <c r="V22" t="n">
         <v>-0.7005</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.3054</v>
+        <v>-6.0451</v>
       </c>
       <c r="E23" t="n">
         <v>-6.7176</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4122</v>
+        <v>0.6725</v>
       </c>
       <c r="G23" t="n">
         <v>-4.054</v>
@@ -2248,13 +2248,13 @@
         <v>1.2487</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2109</v>
+        <v>-0.9506</v>
       </c>
       <c r="T23" t="n">
         <v>-1.0439</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.167</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-28.9027</v>
+        <v>-27.474</v>
       </c>
       <c r="E24" t="n">
-        <v>-25.1957</v>
+        <v>-25.1956</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.707099999999999</v>
+        <v>-2.2782</v>
       </c>
       <c r="G24" t="n">
         <v>-22.7587</v>
@@ -2302,7 +2302,7 @@
         <v>-6.774900000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-4.4275</v>
+        <v>-4.427499999999999</v>
       </c>
       <c r="L24" t="n">
         <v>-2.3471</v>
@@ -2314,7 +2314,7 @@
         <v>-9.431999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-6.5518</v>
+        <v>-6.551799999999999</v>
       </c>
       <c r="P24" t="n">
         <v>-0.000100000000000211</v>
@@ -2326,13 +2326,13 @@
         <v>18.7305</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.834100000000001</v>
+        <v>-5.4053</v>
       </c>
       <c r="T24" t="n">
-        <v>-5.0502</v>
+        <v>-5.0503</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.7838</v>
+        <v>-0.3552000000000002</v>
       </c>
       <c r="V24" t="n">
         <v>0.6898000000000001</v>
